--- a/task501/golden/winter_measles_2027.xlsx
+++ b/task501/golden/winter_measles_2027.xlsx
@@ -94,7 +94,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Reproduction number: the dominant eigenvalue of the next-generation matrix, built from the National Social Contact Survey 2023 (Table 2, contacts per day by age group) and each age group's susceptible share on 1 January 2028, scaled so that a wholly susceptible region gives the R0 of 15 in PS-07 3.2.</t>
+    <t>Reproduction number: the dominant eigenvalue of the next-generation matrix, built from the National Social Contact Survey 2023 diaries kept in school term (2 to 26 May 2023, contacts per day by age band) and each age band's susceptible share on 1 January 2028, scaled so that a wholly susceptible region gives the R0 of 15 in PS-07 3.2. The winter is school term apart from the Christmas and February breaks, and PS-07 3.1 needs the figure below one throughout.</t>
   </si>
   <si>
     <t>Susceptible shares: the national immunity profile (May 2027) by year of birth, weighted by the department's projection of residents at 1 January 2028 (PS-07 3.3, 3.4).</t>
@@ -103,7 +103,7 @@
     <t>Each option takes the options paper's expected people made immune off the susceptibles of its birth years (PS-07 3.5); option E as the paper splits it between those born 1993 to 1997 and 1998 to 2002.</t>
   </si>
   <si>
-    <t>On the region's average immunity alone (94.6 per cent immune, above the 93.3 per cent herd immunity threshold for R0 15) the figure would be 0.8, but the 15 to 19-year-olds have about half their contacts with each other and 11.2 per cent of them are susceptible, against 5.4 per cent across the region.</t>
+    <t>On the region's average immunity alone (95.2 per cent immune, above the 93.3 per cent herd immunity threshold for R0 15) the figure would be 0.7, and on every diary in the survey 0.9. But two thirds of the diaries were kept from 3 July to 18 August 2023, in the school summer holidays, when the 15 to 19-year-olds have under a fifth of their contacts with each other, against more than half in term; 11.2 per cent of them are susceptible, against 4.8 per cent across the region.</t>
   </si>
   <si>
     <t>What each option involves</t>
@@ -148,13 +148,13 @@
     <t>E</t>
   </si>
   <si>
-    <t>Living in the region: active registrations whose local health office, read in the scheme in force when it was recorded, is in the region; LH27 recorded before 1 July 2024 is Monaghan West (circular 03/2024).</t>
+    <t>Living in the region: active registrations with an address in the State whose local health office, read in the scheme in force when it was recorded, is in the region; LH27 recorded before 1 July 2024 is Monaghan West (circular 03/2024). Records with a UK postcode, pupils living in Northern Ireland, are not living in the region.</t>
   </si>
   <si>
     <t>Valid doses: MMR events re-pointed through the register's merges to the registration they now belong to, less GP return lines the query log shows replaced or withdrawn, counted under the guidelines' 12.5 (on or after the first birthday, at least 28 days after the previous valid dose), given on or before 30 June 2027.</t>
   </si>
   <si>
-    <t>Cases: confirmed cases, one per person and illness; the 2019 outbreak's cases back-entered to the outbreak module in May 2021 (legacy number in the comments) are counted once, with their migrated records. Option E includes option D's birth years.</t>
+    <t>Cases: confirmed cases, one per person and illness: the 2019 outbreak's cases back-entered to the outbreak module in May 2021 (legacy number in the comments) count once with their migrated records, and a case notified twice (the same date of birth, sex and rash onset) once. Option E includes option D's birth years.</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="8">
-        <v>820</v>
+        <v>790</v>
       </c>
       <c r="D9" s="6">
         <v>1.3</v>
@@ -654,7 +654,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="10">
-        <v>1740</v>
+        <v>1470</v>
       </c>
       <c r="D10" s="11">
         <v>0.9</v>
@@ -671,7 +671,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="8">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="D11" s="6">
         <v>1.3</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="8">
-        <v>1980</v>
+        <v>1590</v>
       </c>
       <c r="D12" s="6">
         <v>1.3</v>
@@ -705,7 +705,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="8">
-        <v>2890</v>
+        <v>2250</v>
       </c>
       <c r="D13" s="6">
         <v>1.3</v>
@@ -810,10 +810,10 @@
         <v>35346</v>
       </c>
       <c r="D5" s="8">
-        <v>3542</v>
+        <v>3545</v>
       </c>
       <c r="E5" s="8">
-        <v>4724</v>
+        <v>4720</v>
       </c>
       <c r="F5" s="8">
         <v>9</v>
@@ -833,10 +833,10 @@
         <v>33217</v>
       </c>
       <c r="D6" s="8">
-        <v>4285</v>
+        <v>4286</v>
       </c>
       <c r="E6" s="8">
-        <v>6094</v>
+        <v>6091</v>
       </c>
       <c r="F6" s="8">
         <v>10</v>
@@ -856,7 +856,7 @@
         <v>29398</v>
       </c>
       <c r="D7" s="8">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="E7" s="8">
         <v>3960</v>
@@ -902,10 +902,10 @@
         <v>57865</v>
       </c>
       <c r="D9" s="8">
-        <v>8530</v>
+        <v>8526</v>
       </c>
       <c r="E9" s="8">
-        <v>11788</v>
+        <v>11793</v>
       </c>
       <c r="F9" s="8">
         <v>16</v>
